--- a/VerveStacks_KEN_grids_kan10/SuppXLS/Scen_TSParameters_ts_40c.xlsx
+++ b/VerveStacks_KEN_grids_kan10/SuppXLS/Scen_TSParameters_ts_40c.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_KEN_grids_kan10\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8C63C804-A5A8-4397-B0FD-81F16E1CFB6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{97B47123-96EF-4665-870E-9D2C8152599C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -747,13 +747,13 @@
     <t>D</t>
   </si>
   <si>
-    <t>S02aH04,S02aH05,S04aH02,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S01aH04,S01aH07,S02aH07,S04aH06,S03aH03,S01aH02,S04aH04,S02aH06,S03aH05,S03aH08,S04aH07,S01aH03,S04aH05,S04aH08,S03aH02,S01aH06,S02aH03,S04aH03,S03aH04,S02aH02</t>
+    <t>S01aH02,S04aH04,S02aH04,S02aH05,S03aH02,S03aH03,S04aH03,S04aH02,S04aH06,S01aH04,S01aH07,S02aH07,S02aH02,S02aH06,S03aH05,S03aH08,S04aH07,S03aH04,S01aH03,S04aH05,S04aH08,S01aH06,S02aH03,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>S03aH08,S03aH10,S04aH08,S01aH10,S03aH02,S01aH02,S01aH09,S02aH02,S04aH10,S01aH08,S02aH08,S03aH09,S04aH02,S01aH01,S04aH01,S02aH01,S02aH10,S02aH09,S04aH09,S03aH01</t>
+    <t>S01aH08,S02aH08,S03aH08,S03aH10,S04aH02,S02aH02,S04aH10,S02aH01,S02aH10,S01aH10,S03aH02,S01aH09,S03aH01,S04aH08,S03aH09,S02aH09,S04aH09,S01aH01,S04aH01,S01aH02</t>
   </si>
   <si>
     <t>elc_buildings</t>
@@ -1348,7 +1348,7 @@
       </c>
       <c r="H23" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,3,FALSE)</f>
-        <v>S03aH08,S03aH10,S04aH08,S01aH10,S03aH02,S01aH02,S01aH09,S02aH02,S04aH10,S01aH08,S02aH08,S03aH09,S04aH02,S01aH01,S04aH01,S02aH01,S02aH10,S02aH09,S04aH09,S03aH01</v>
+        <v>S01aH08,S02aH08,S03aH08,S03aH10,S04aH02,S02aH02,S04aH10,S02aH01,S02aH10,S01aH10,S03aH02,S01aH09,S03aH01,S04aH08,S03aH09,S02aH09,S04aH09,S01aH01,S04aH01,S01aH02</v>
       </c>
       <c r="I23">
         <f>1+I24</f>
@@ -1380,7 +1380,7 @@
       </c>
       <c r="H24" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,2,FALSE)</f>
-        <v>S02aH04,S02aH05,S04aH02,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S01aH04,S01aH07,S02aH07,S04aH06,S03aH03,S01aH02,S04aH04,S02aH06,S03aH05,S03aH08,S04aH07,S01aH03,S04aH05,S04aH08,S03aH02,S01aH06,S02aH03,S04aH03,S03aH04,S02aH02</v>
+        <v>S01aH02,S04aH04,S02aH04,S02aH05,S03aH02,S03aH03,S04aH03,S04aH02,S04aH06,S01aH04,S01aH07,S02aH07,S02aH02,S02aH06,S03aH05,S03aH08,S04aH07,S03aH04,S01aH03,S04aH05,S04aH08,S01aH06,S02aH03,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07</v>
       </c>
       <c r="I24">
         <f>-$I$17</f>
@@ -1476,7 +1476,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4CE8C3DC-0858-4336-B27D-4CA1CD21608E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{101EEC4F-9600-49D9-88C4-1304D29174B8}">
   <dimension ref="A9:G20"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1614,7 +1614,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0266C73A-38BC-4ADB-BA92-EFEC1D20605D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96084D21-86D6-4931-B8D6-4EE5E0A0C4FA}">
   <dimension ref="B9:O1130"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -33196,7 +33196,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE749776-27A2-47E2-BF14-069E60546CE3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A8E370D-0BE9-4740-8B52-D455ADD3F728}">
   <dimension ref="B9:FT71"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -50542,7 +50542,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BAD89735-5ACF-4AD6-BE62-6D58ED64874E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DDEE2CB0-D5CD-4524-947D-8183E322B141}">
   <dimension ref="B9:E50"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -51132,7 +51132,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5AA639F0-AB43-427C-BAF5-582C3BC48DE4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FBB890C4-FDF4-429F-B8E1-B9C87AAA6788}">
   <dimension ref="B9:D90"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -52039,7 +52039,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{72C5CE72-1E4B-462E-B008-B233902C21E0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6635ADC2-45D6-4717-A773-BA00B566E3F7}">
   <dimension ref="B9:D50"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -52506,7 +52506,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49AB0A9D-8569-42B0-B9CA-22C1B3088CF4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AEC35E95-27D0-4F3D-AC32-FE732E3ADA68}">
   <dimension ref="B9:E126"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -52580,7 +52580,7 @@
         <v>45</v>
       </c>
       <c r="D14">
-        <v>0.60353333333333326</v>
+        <v>0.60353333333333337</v>
       </c>
       <c r="E14" t="s">
         <v>243</v>
@@ -52622,7 +52622,7 @@
         <v>43</v>
       </c>
       <c r="D17">
-        <v>0.46400000000000002</v>
+        <v>0.46399999999999997</v>
       </c>
       <c r="E17" t="s">
         <v>243</v>
@@ -52748,7 +52748,7 @@
         <v>45</v>
       </c>
       <c r="D26">
-        <v>0.41706666666666664</v>
+        <v>0.4170666666666667</v>
       </c>
       <c r="E26" t="s">
         <v>243</v>
@@ -52790,7 +52790,7 @@
         <v>43</v>
       </c>
       <c r="D29">
-        <v>0.47366666666666662</v>
+        <v>0.47366666666666668</v>
       </c>
       <c r="E29" t="s">
         <v>243</v>
@@ -52944,7 +52944,7 @@
         <v>41</v>
       </c>
       <c r="D40">
-        <v>0.35449999999999998</v>
+        <v>0.35450000000000004</v>
       </c>
       <c r="E40" t="s">
         <v>243</v>
@@ -52958,7 +52958,7 @@
         <v>43</v>
       </c>
       <c r="D41">
-        <v>0.42979999999999996</v>
+        <v>0.42980000000000002</v>
       </c>
       <c r="E41" t="s">
         <v>243</v>
@@ -53014,7 +53014,7 @@
         <v>43</v>
       </c>
       <c r="D45">
-        <v>0.36883333333333329</v>
+        <v>0.36883333333333335</v>
       </c>
       <c r="E45" t="s">
         <v>243</v>
@@ -53028,7 +53028,7 @@
         <v>45</v>
       </c>
       <c r="D46">
-        <v>0.45263333333333339</v>
+        <v>0.45263333333333328</v>
       </c>
       <c r="E46" t="s">
         <v>243</v>
@@ -53196,7 +53196,7 @@
         <v>45</v>
       </c>
       <c r="D58">
-        <v>0.35393333333333338</v>
+        <v>0.35393333333333327</v>
       </c>
       <c r="E58" t="s">
         <v>243</v>
@@ -53364,7 +53364,7 @@
         <v>45</v>
       </c>
       <c r="D70">
-        <v>0.40836666666666671</v>
+        <v>0.4083666666666666</v>
       </c>
       <c r="E70" t="s">
         <v>243</v>
@@ -53504,7 +53504,7 @@
         <v>41</v>
       </c>
       <c r="D80">
-        <v>0.39866666666666667</v>
+        <v>0.39866666666666672</v>
       </c>
       <c r="E80" t="s">
         <v>243</v>
@@ -53518,7 +53518,7 @@
         <v>43</v>
       </c>
       <c r="D81">
-        <v>0.53039999999999987</v>
+        <v>0.53039999999999998</v>
       </c>
       <c r="E81" t="s">
         <v>243</v>
@@ -53686,7 +53686,7 @@
         <v>43</v>
       </c>
       <c r="D93">
-        <v>0.49020000000000002</v>
+        <v>0.49019999999999997</v>
       </c>
       <c r="E93" t="s">
         <v>243</v>
@@ -53742,7 +53742,7 @@
         <v>43</v>
       </c>
       <c r="D97">
-        <v>0.47839999999999999</v>
+        <v>0.47839999999999994</v>
       </c>
       <c r="E97" t="s">
         <v>243</v>
@@ -53756,7 +53756,7 @@
         <v>45</v>
       </c>
       <c r="D98">
-        <v>0.42363333333333336</v>
+        <v>0.42363333333333331</v>
       </c>
       <c r="E98" t="s">
         <v>243</v>
@@ -53798,7 +53798,7 @@
         <v>43</v>
       </c>
       <c r="D101">
-        <v>0.5383</v>
+        <v>0.53829999999999989</v>
       </c>
       <c r="E101" t="s">
         <v>243</v>
@@ -53966,7 +53966,7 @@
         <v>43</v>
       </c>
       <c r="D113">
-        <v>0.43929999999999997</v>
+        <v>0.43930000000000002</v>
       </c>
       <c r="E113" t="s">
         <v>243</v>
@@ -53980,7 +53980,7 @@
         <v>45</v>
       </c>
       <c r="D114">
-        <v>0.45659999999999995</v>
+        <v>0.45660000000000006</v>
       </c>
       <c r="E114" t="s">
         <v>243</v>
@@ -54036,7 +54036,7 @@
         <v>45</v>
       </c>
       <c r="D118">
-        <v>0.38423333333333326</v>
+        <v>0.38423333333333337</v>
       </c>
       <c r="E118" t="s">
         <v>243</v>
@@ -54078,7 +54078,7 @@
         <v>43</v>
       </c>
       <c r="D121">
-        <v>0.4809666666666666</v>
+        <v>0.48096666666666671</v>
       </c>
       <c r="E121" t="s">
         <v>243</v>
